--- a/data/final/03_releases_gsynth.xlsx
+++ b/data/final/03_releases_gsynth.xlsx
@@ -397,16 +397,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C2">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D2">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E2">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F2">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="3">
@@ -419,16 +419,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C3">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D3">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E3">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068412</v>
       </c>
       <c r="F3">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834259</v>
       </c>
     </row>
     <row r="4">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.01394696833882924</v>
+        <v>0.01394696833882919</v>
       </c>
       <c r="C4">
-        <v>0.4735488808787691</v>
+        <v>0.463065030304918</v>
       </c>
       <c r="D4">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E4">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068416</v>
       </c>
       <c r="F4">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834254</v>
       </c>
     </row>
     <row r="5">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.01394696833882923</v>
+        <v>0.01394696833882924</v>
       </c>
       <c r="C5">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D5">
-        <v>0.01945952581635922</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E5">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068412</v>
       </c>
       <c r="F5">
-        <v>0.05208693809512069</v>
+        <v>0.05119855293834259</v>
       </c>
     </row>
     <row r="6">
@@ -485,16 +485,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C6">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D6">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E6">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068412</v>
       </c>
       <c r="F6">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834259</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.01394696833882927</v>
+        <v>0.01394696833882924</v>
       </c>
       <c r="C7">
-        <v>0.473548880878768</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D7">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E7">
-        <v>-0.02419300141746219</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F7">
-        <v>0.05208693809512074</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="8">
@@ -529,16 +529,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C8">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D8">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E8">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F8">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="9">
@@ -551,16 +551,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C9">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D9">
-        <v>0.01945952581635922</v>
+        <v>0.01900625975443893</v>
       </c>
       <c r="E9">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F9">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="10">
@@ -573,16 +573,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C10">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D10">
-        <v>0.01945952581635922</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E10">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068412</v>
       </c>
       <c r="F10">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834259</v>
       </c>
     </row>
     <row r="11">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.01394696833882923</v>
+        <v>0.01394696833882919</v>
       </c>
       <c r="C11">
-        <v>0.4735488808787693</v>
+        <v>0.4630650303049182</v>
       </c>
       <c r="D11">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E11">
-        <v>-0.02419300141746224</v>
+        <v>-0.02330461626068418</v>
       </c>
       <c r="F11">
-        <v>0.05208693809512071</v>
+        <v>0.05119855293834256</v>
       </c>
     </row>
     <row r="12">
@@ -617,16 +617,16 @@
         <v>0.01394696833882924</v>
       </c>
       <c r="C12">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D12">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443893</v>
       </c>
       <c r="E12">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F12">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="13">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.01394696833882927</v>
+        <v>0.01394696833882924</v>
       </c>
       <c r="C13">
-        <v>0.473548880878768</v>
+        <v>0.4630650303049166</v>
       </c>
       <c r="D13">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443893</v>
       </c>
       <c r="E13">
-        <v>-0.02419300141746219</v>
+        <v>-0.02330461626068413</v>
       </c>
       <c r="F13">
-        <v>0.05208693809512074</v>
+        <v>0.05119855293834261</v>
       </c>
     </row>
     <row r="14">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.01394696833882924</v>
+        <v>0.01394696833882919</v>
       </c>
       <c r="C14">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049182</v>
       </c>
       <c r="D14">
-        <v>0.01945952581635923</v>
+        <v>0.01900625975443892</v>
       </c>
       <c r="E14">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068417</v>
       </c>
       <c r="F14">
-        <v>0.0520869380951207</v>
+        <v>0.05119855293834255</v>
       </c>
     </row>
     <row r="15">
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.01394696833882923</v>
+        <v>0.01394696833882919</v>
       </c>
       <c r="C15">
-        <v>0.4735488808787691</v>
+        <v>0.4630650303049184</v>
       </c>
       <c r="D15">
-        <v>0.01945952581635922</v>
+        <v>0.01900625975443893</v>
       </c>
       <c r="E15">
-        <v>-0.02419300141746222</v>
+        <v>-0.02330461626068418</v>
       </c>
       <c r="F15">
-        <v>0.05208693809512069</v>
+        <v>0.05119855293834256</v>
       </c>
     </row>
     <row r="16">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.006609894679441826</v>
+        <v>0.006609894679441832</v>
       </c>
       <c r="C16">
-        <v>0.7530974918806854</v>
+        <v>0.7461224200207992</v>
       </c>
       <c r="D16">
-        <v>0.02101329722688182</v>
+        <v>0.02041625555372563</v>
       </c>
       <c r="E16">
-        <v>-0.03457541108168192</v>
+        <v>-0.03340523090502624</v>
       </c>
       <c r="F16">
-        <v>0.04779520044056557</v>
+        <v>0.04662502026390991</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.01356078850452214</v>
+        <v>0.01356078850452209</v>
       </c>
       <c r="C17">
-        <v>0.4860501172669125</v>
+        <v>0.4756323037867562</v>
       </c>
       <c r="D17">
-        <v>0.01946697388870892</v>
+        <v>0.01901014051160982</v>
       </c>
       <c r="E17">
-        <v>-0.02459377920532897</v>
+        <v>-0.02369840223927898</v>
       </c>
       <c r="F17">
-        <v>0.05171535621437325</v>
+        <v>0.05081997924832317</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.02268670147136042</v>
+        <v>-0.02268670147136041</v>
       </c>
       <c r="C18">
-        <v>0.4327427375486592</v>
+        <v>0.4396322231682546</v>
       </c>
       <c r="D18">
-        <v>0.02891842201332572</v>
+        <v>0.02935595032136587</v>
       </c>
       <c r="E18">
-        <v>-0.07936576710720909</v>
+        <v>-0.08022330683318452</v>
       </c>
       <c r="F18">
-        <v>0.03399236416448825</v>
+        <v>0.0348499038904637</v>
       </c>
     </row>
     <row r="19">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.005401291991382606</v>
+        <v>0.005401291991382497</v>
       </c>
       <c r="C19">
-        <v>0.8346422020272457</v>
+        <v>0.8323443600727971</v>
       </c>
       <c r="D19">
-        <v>0.0258742615744704</v>
+        <v>0.02551440241900968</v>
       </c>
       <c r="E19">
-        <v>-0.04531132882114799</v>
+        <v>-0.04460601783693809</v>
       </c>
       <c r="F19">
-        <v>0.0561139128039132</v>
+        <v>0.05540860181970308</v>
       </c>
     </row>
     <row r="20">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.003307838902698289</v>
+        <v>-0.003307838902698263</v>
       </c>
       <c r="C20">
-        <v>0.9255627469237162</v>
+        <v>0.926234327935104</v>
       </c>
       <c r="D20">
-        <v>0.03540483842860043</v>
+        <v>0.035728108134565</v>
       </c>
       <c r="E20">
-        <v>-0.07270004710121479</v>
+        <v>-0.07333364408219817</v>
       </c>
       <c r="F20">
-        <v>0.06608436929581822</v>
+        <v>0.06671796627680165</v>
       </c>
     </row>
     <row r="21">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.03849619360732484</v>
+        <v>-0.03849619360732478</v>
       </c>
       <c r="C21">
-        <v>0.3845361895175092</v>
+        <v>0.3770578393047126</v>
       </c>
       <c r="D21">
-        <v>0.04427044911170103</v>
+        <v>0.04358074636890772</v>
       </c>
       <c r="E21">
-        <v>-0.1252646794456721</v>
+        <v>-0.1239128869097586</v>
       </c>
       <c r="F21">
-        <v>0.04827229223102239</v>
+        <v>0.04692049969510906</v>
       </c>
     </row>
     <row r="22">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.0759507995793641</v>
+        <v>-0.07595079957936388</v>
       </c>
       <c r="C22">
-        <v>0.2627821915420836</v>
+        <v>0.2714328823979784</v>
       </c>
       <c r="D22">
-        <v>0.06782293717354582</v>
+        <v>0.06906069858996371</v>
       </c>
       <c r="E22">
-        <v>-0.2088813137652367</v>
+        <v>-0.2113072815628688</v>
       </c>
       <c r="F22">
-        <v>0.05697971460650847</v>
+        <v>0.05940568240414104</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.03062611181763621</v>
+        <v>-0.03062611181763601</v>
       </c>
       <c r="C23">
-        <v>0.5949705255298823</v>
+        <v>0.5829155222459335</v>
       </c>
       <c r="D23">
-        <v>0.05760610599636854</v>
+        <v>0.0557719549038789</v>
       </c>
       <c r="E23">
-        <v>-0.1435320048601154</v>
+        <v>-0.1399371347766307</v>
       </c>
       <c r="F23">
-        <v>0.08227978122484295</v>
+        <v>0.07868491114135864</v>
       </c>
     </row>
     <row r="24">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.067429881367721</v>
+        <v>-0.06742988136772067</v>
       </c>
       <c r="C24">
-        <v>0.2136412959772254</v>
+        <v>0.23067150173341</v>
       </c>
       <c r="D24">
-        <v>0.05422086564168736</v>
+        <v>0.05625575143389138</v>
       </c>
       <c r="E24">
-        <v>-0.1737008252360134</v>
+        <v>-0.1776891281013853</v>
       </c>
       <c r="F24">
-        <v>0.03884106250057143</v>
+        <v>0.04282936536594391</v>
       </c>
     </row>
     <row r="25">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.0131825837168528</v>
+        <v>-0.01318258371685252</v>
       </c>
       <c r="C25">
-        <v>0.8603793769824291</v>
+        <v>0.8620344761824525</v>
       </c>
       <c r="D25">
-        <v>0.07494735218716159</v>
+        <v>0.07585572896426841</v>
       </c>
       <c r="E25">
-        <v>-0.1600766947403287</v>
+        <v>-0.1618570805078504</v>
       </c>
       <c r="F25">
-        <v>0.1337115273066231</v>
+        <v>0.1354919130741453</v>
       </c>
     </row>
     <row r="26">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.02486797025225008</v>
+        <v>-0.02486797025224978</v>
       </c>
       <c r="C26">
-        <v>0.7939873845429073</v>
+        <v>0.796293297806723</v>
       </c>
       <c r="D26">
-        <v>0.09522984142484858</v>
+        <v>0.09633251613256898</v>
       </c>
       <c r="E26">
-        <v>-0.2115150296984137</v>
+        <v>-0.2136762324122086</v>
       </c>
       <c r="F26">
-        <v>0.1617790891939136</v>
+        <v>0.1639402919077091</v>
       </c>
     </row>
     <row r="27">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.01180728505199429</v>
+        <v>-0.01180728505199405</v>
       </c>
       <c r="C27">
-        <v>0.8780487295885882</v>
+        <v>0.8782866704139689</v>
       </c>
       <c r="D27">
-        <v>0.07694886561040984</v>
+        <v>0.07710048013454354</v>
       </c>
       <c r="E27">
-        <v>-0.1626242902996103</v>
+        <v>-0.1629214493064453</v>
       </c>
       <c r="F27">
-        <v>0.1390097201956217</v>
+        <v>0.1393068792024572</v>
       </c>
     </row>
     <row r="28">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.02992048006397166</v>
+        <v>0.02992048006397182</v>
       </c>
       <c r="C28">
-        <v>0.7693488358653118</v>
+        <v>0.7741101696876185</v>
       </c>
       <c r="D28">
-        <v>0.1020387112770488</v>
+        <v>0.1042515235526713</v>
       </c>
       <c r="E28">
-        <v>-0.1700717190679249</v>
+        <v>-0.1744087514326931</v>
       </c>
       <c r="F28">
-        <v>0.2299126791958682</v>
+        <v>0.2342497115606367</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.05268298291442485</v>
+        <v>0.05268298291442516</v>
       </c>
       <c r="C29">
-        <v>0.5325233003491165</v>
+        <v>0.5360312000104701</v>
       </c>
       <c r="D29">
-        <v>0.08440637671782551</v>
+        <v>0.08513380139845439</v>
       </c>
       <c r="E29">
-        <v>-0.1127504755180332</v>
+        <v>-0.1141762016935311</v>
       </c>
       <c r="F29">
-        <v>0.2181164413468829</v>
+        <v>0.2195421675223814</v>
       </c>
     </row>
     <row r="30">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.1702488212114522</v>
+        <v>-0.1702488212114518</v>
       </c>
       <c r="C30">
-        <v>0.1503271855039192</v>
+        <v>0.1440789674933289</v>
       </c>
       <c r="D30">
-        <v>0.1183617721055837</v>
+        <v>0.1165474300364149</v>
       </c>
       <c r="E30">
-        <v>-0.4022336316847338</v>
+        <v>-0.3986775865735266</v>
       </c>
       <c r="F30">
-        <v>0.06173598926182947</v>
+        <v>0.05817994415062294</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.05861978411412783</v>
+        <v>-0.05861978411412753</v>
       </c>
       <c r="C31">
-        <v>0.4552945351967934</v>
+        <v>0.4537390253373852</v>
       </c>
       <c r="D31">
-        <v>0.07851381872703497</v>
+        <v>0.07824357985595699</v>
       </c>
       <c r="E31">
-        <v>-0.2125040411078228</v>
+        <v>-0.2119743826532869</v>
       </c>
       <c r="F31">
-        <v>0.0952644728795671</v>
+        <v>0.09473481442503182</v>
       </c>
     </row>
     <row r="32">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.4447171562686009</v>
+        <v>0.4447171562686012</v>
       </c>
       <c r="C32">
-        <v>0.2229942143062467</v>
+        <v>0.2092545664430059</v>
       </c>
       <c r="D32">
-        <v>0.3649395970727442</v>
+        <v>0.3541819399983652</v>
       </c>
       <c r="E32">
-        <v>-0.2705513105265364</v>
+        <v>-0.2494666901027208</v>
       </c>
       <c r="F32">
-        <v>1.159985623063738</v>
+        <v>1.138901002639923</v>
       </c>
     </row>
     <row r="33">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.0288758367277472</v>
+        <v>-0.02887583672774709</v>
       </c>
       <c r="C33">
-        <v>0.7700115060531145</v>
+        <v>0.78191492001187</v>
       </c>
       <c r="D33">
-        <v>0.09876813501922958</v>
+        <v>0.1043110122984587</v>
       </c>
       <c r="E33">
-        <v>-0.2224578241856264</v>
+        <v>-0.2333216640236408</v>
       </c>
       <c r="F33">
-        <v>0.164706150730132</v>
+        <v>0.1755699905681466</v>
       </c>
     </row>
     <row r="34">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.06242389432278122</v>
+        <v>-0.06242389432278119</v>
       </c>
       <c r="C34">
-        <v>0.4461027059646441</v>
+        <v>0.4830561879982098</v>
       </c>
       <c r="D34">
-        <v>0.0819288135479906</v>
+        <v>0.08899955645417347</v>
       </c>
       <c r="E34">
-        <v>-0.22300141817294</v>
+        <v>-0.2368598196130005</v>
       </c>
       <c r="F34">
-        <v>0.09815362952737755</v>
+        <v>0.1120120309674381</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.09997494543186645</v>
+        <v>-0.09997494543186641</v>
       </c>
       <c r="C35">
-        <v>0.3428871801310474</v>
+        <v>0.3468901161023215</v>
       </c>
       <c r="D35">
-        <v>0.1054058767857588</v>
+        <v>0.1062841244699386</v>
       </c>
       <c r="E35">
-        <v>-0.3065666676908201</v>
+        <v>-0.3082880015213182</v>
       </c>
       <c r="F35">
-        <v>0.1066167768270872</v>
+        <v>0.1083381106575854</v>
       </c>
     </row>
     <row r="36">
@@ -1145,16 +1145,16 @@
         <v>0.08940695279462514</v>
       </c>
       <c r="C36">
-        <v>0.298924277614399</v>
+        <v>0.2863105356192208</v>
       </c>
       <c r="D36">
-        <v>0.08607225550109762</v>
+        <v>0.08385175376793119</v>
       </c>
       <c r="E36">
-        <v>-0.0792915680556557</v>
+        <v>-0.07493946463104072</v>
       </c>
       <c r="F36">
-        <v>0.258105473644906</v>
+        <v>0.253753370220291</v>
       </c>
     </row>
     <row r="37">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.06516915995029109</v>
+        <v>0.06516915995029103</v>
       </c>
       <c r="C37">
-        <v>0.5686223021636527</v>
+        <v>0.5618176136496589</v>
       </c>
       <c r="D37">
-        <v>0.1143154789839299</v>
+        <v>0.1123327597048581</v>
       </c>
       <c r="E37">
-        <v>-0.158885061733657</v>
+        <v>-0.1549990033552231</v>
       </c>
       <c r="F37">
-        <v>0.2892233816342392</v>
+        <v>0.2853373232558051</v>
       </c>
     </row>
     <row r="38">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.02619425457536401</v>
+        <v>-0.02619425457536411</v>
       </c>
       <c r="C38">
-        <v>0.7663020560563396</v>
+        <v>0.7548493151018711</v>
       </c>
       <c r="D38">
-        <v>0.08813222163100146</v>
+        <v>0.08388829407025586</v>
       </c>
       <c r="E38">
-        <v>-0.1989302348496287</v>
+        <v>-0.1906122896775705</v>
       </c>
       <c r="F38">
-        <v>0.1465417256989007</v>
+        <v>0.1382237805268423</v>
       </c>
     </row>
     <row r="39">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.09666113826612406</v>
+        <v>-0.09666113826612432</v>
       </c>
       <c r="C39">
-        <v>0.2244997096622057</v>
+        <v>0.2129649073612194</v>
       </c>
       <c r="D39">
-        <v>0.07957943360179613</v>
+        <v>0.07761116572216227</v>
       </c>
       <c r="E39">
-        <v>-0.252633962035741</v>
+        <v>-0.2487762278797319</v>
       </c>
       <c r="F39">
-        <v>0.0593116855034929</v>
+        <v>0.05545395134748324</v>
       </c>
     </row>
     <row r="40">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.1433729254311844</v>
+        <v>0.1433729254311842</v>
       </c>
       <c r="C40">
-        <v>0.1765133379801886</v>
+        <v>0.1733478227259173</v>
       </c>
       <c r="D40">
-        <v>0.1060789055356665</v>
+        <v>0.1053031858756086</v>
       </c>
       <c r="E40">
-        <v>-0.06453790893814834</v>
+        <v>-0.06301752634233562</v>
       </c>
       <c r="F40">
-        <v>0.3512837598005172</v>
+        <v>0.349763377204704</v>
       </c>
     </row>
     <row r="41">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.005856736826020487</v>
+        <v>0.005856736826020261</v>
       </c>
       <c r="C41">
-        <v>0.9384462314255508</v>
+        <v>0.9401747182106956</v>
       </c>
       <c r="D41">
-        <v>0.07584197807508537</v>
+        <v>0.07803752264436084</v>
       </c>
       <c r="E41">
-        <v>-0.1427908087174232</v>
+        <v>-0.1470939969996559</v>
       </c>
       <c r="F41">
-        <v>0.1545042823694642</v>
+        <v>0.1588074706516964</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.03841439831511177</v>
+        <v>-0.03841439831511203</v>
       </c>
       <c r="C42">
-        <v>0.7001124178735949</v>
+        <v>0.7106279427692497</v>
       </c>
       <c r="D42">
-        <v>0.09973395157855247</v>
+        <v>0.1035392596517348</v>
       </c>
       <c r="E42">
-        <v>-0.2338893514449362</v>
+        <v>-0.2413476182184534</v>
       </c>
       <c r="F42">
-        <v>0.1570605548147127</v>
+        <v>0.1645188215882293</v>
       </c>
     </row>
     <row r="43">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.09456117223976213</v>
+        <v>-0.09456117223976235</v>
       </c>
       <c r="C43">
-        <v>0.2313208714453139</v>
+        <v>0.2012313841874009</v>
       </c>
       <c r="D43">
-        <v>0.07900089721082586</v>
+        <v>0.07398856507918969</v>
       </c>
       <c r="E43">
-        <v>-0.2494000855193316</v>
+        <v>-0.239576095062772</v>
       </c>
       <c r="F43">
-        <v>0.06027774103980732</v>
+        <v>0.05045375058324733</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.000515911518429625</v>
+        <v>-0.000515911518429761</v>
       </c>
       <c r="C44">
-        <v>0.9942993465862482</v>
+        <v>0.9936270317889719</v>
       </c>
       <c r="D44">
-        <v>0.07220827214861525</v>
+        <v>0.06459054002873939</v>
       </c>
       <c r="E44">
-        <v>-0.1420415243155821</v>
+        <v>-0.1271110437167516</v>
       </c>
       <c r="F44">
-        <v>0.1410097012787229</v>
+        <v>0.1260792206798921</v>
       </c>
     </row>
     <row r="45">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.005145402480384402</v>
+        <v>0.005145402480384319</v>
       </c>
       <c r="C45">
-        <v>0.9509964133065361</v>
+        <v>0.941683669237235</v>
       </c>
       <c r="D45">
-        <v>0.08372559465639322</v>
+        <v>0.07033670296556578</v>
       </c>
       <c r="E45">
-        <v>-0.1589537476303454</v>
+        <v>-0.1327120021234162</v>
       </c>
       <c r="F45">
-        <v>0.1692445525911142</v>
+        <v>0.1430028070841848</v>
       </c>
     </row>
     <row r="46">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.07577111572467128</v>
+        <v>-0.07577111572467136</v>
       </c>
       <c r="C46">
-        <v>0.3319909669611405</v>
+        <v>0.3397310711387116</v>
       </c>
       <c r="D46">
-        <v>0.0781055821901132</v>
+        <v>0.07936668402079751</v>
       </c>
       <c r="E46">
-        <v>-0.2288552438088262</v>
+        <v>-0.2313269579778051</v>
       </c>
       <c r="F46">
-        <v>0.07731301235948361</v>
+        <v>0.07978472652846232</v>
       </c>
     </row>
     <row r="47">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.0874120540470967</v>
+        <v>-0.0874120540470968</v>
       </c>
       <c r="C47">
-        <v>0.2930944158383832</v>
+        <v>0.2900216576360279</v>
       </c>
       <c r="D47">
-        <v>0.08314208243139154</v>
+        <v>0.08261430214738544</v>
       </c>
       <c r="E47">
-        <v>-0.2503675412122844</v>
+        <v>-0.2493331108638823</v>
       </c>
       <c r="F47">
-        <v>0.07554343311809103</v>
+        <v>0.07450900276968865</v>
       </c>
     </row>
     <row r="48">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.007262123448302793</v>
+        <v>0.007262123448302649</v>
       </c>
       <c r="C48">
-        <v>0.9502029193261017</v>
+        <v>0.9497341132311168</v>
       </c>
       <c r="D48">
-        <v>0.1162833592883845</v>
+        <v>0.115197421799127</v>
       </c>
       <c r="E48">
-        <v>-0.2206490727582619</v>
+        <v>-0.2185206743898555</v>
       </c>
       <c r="F48">
-        <v>0.2351733196548675</v>
+        <v>0.2330449212864608</v>
       </c>
     </row>
     <row r="49">
@@ -1431,16 +1431,16 @@
         <v>0.104123935804985</v>
       </c>
       <c r="C49">
-        <v>0.5589646443188068</v>
+        <v>0.5302072118113856</v>
       </c>
       <c r="D49">
-        <v>0.1781784566189523</v>
+        <v>0.1658844014300428</v>
       </c>
       <c r="E49">
-        <v>-0.2450994219890938</v>
+        <v>-0.2210035165948834</v>
       </c>
       <c r="F49">
-        <v>0.4533472935990638</v>
+        <v>0.4292513882048534</v>
       </c>
     </row>
     <row r="50">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.006247800367372283</v>
+        <v>-0.006247800367372288</v>
       </c>
       <c r="C50">
-        <v>0.9239760172495108</v>
+        <v>0.9162072720579471</v>
       </c>
       <c r="D50">
-        <v>0.06547233913441633</v>
+        <v>0.05938273820223153</v>
       </c>
       <c r="E50">
-        <v>-0.1345712270544206</v>
+        <v>-0.1226358285471168</v>
       </c>
       <c r="F50">
-        <v>0.122075626319676</v>
+        <v>0.1101402278123723</v>
       </c>
     </row>
     <row r="51">
@@ -1472,19 +1472,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.1048050357232298</v>
+        <v>0.10480503572323</v>
       </c>
       <c r="C51">
-        <v>0.3683427310242795</v>
+        <v>0.3194641881781339</v>
       </c>
       <c r="D51">
-        <v>0.1165041472617009</v>
+        <v>0.1052724911030508</v>
       </c>
       <c r="E51">
-        <v>-0.1235388969592547</v>
+        <v>-0.1015252554015626</v>
       </c>
       <c r="F51">
-        <v>0.3331489684057143</v>
+        <v>0.3111353268480227</v>
       </c>
     </row>
     <row r="52">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.0280765382399588</v>
+        <v>-0.02807653823995872</v>
       </c>
       <c r="C52">
-        <v>0.7758631684735811</v>
+        <v>0.7688205260999235</v>
       </c>
       <c r="D52">
-        <v>0.09861308524871472</v>
+        <v>0.09552505661848511</v>
       </c>
       <c r="E52">
-        <v>-0.2213546337318177</v>
+        <v>-0.215302208833339</v>
       </c>
       <c r="F52">
-        <v>0.1652015572519001</v>
+        <v>0.1591491323534215</v>
       </c>
     </row>
     <row r="53">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.1160430815925474</v>
+        <v>-0.1160430815925475</v>
       </c>
       <c r="C53">
-        <v>0.2989807711214276</v>
+        <v>0.3338235549157447</v>
       </c>
       <c r="D53">
-        <v>0.1117279721559866</v>
+        <v>0.1200725975216668</v>
       </c>
       <c r="E53">
-        <v>-0.335025883083975</v>
+        <v>-0.3513810482651877</v>
       </c>
       <c r="F53">
-        <v>0.1029397198988801</v>
+        <v>0.1192948850800928</v>
       </c>
     </row>
     <row r="54">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.1665181350347159</v>
+        <v>-0.1665181350347158</v>
       </c>
       <c r="C54">
-        <v>0.1746806182199121</v>
+        <v>0.1543509493912465</v>
       </c>
       <c r="D54">
-        <v>0.1226818625355754</v>
+        <v>0.1169097946974712</v>
       </c>
       <c r="E54">
-        <v>-0.4069701671607374</v>
+        <v>-0.395657122081731</v>
       </c>
       <c r="F54">
-        <v>0.07393389709130566</v>
+        <v>0.06262085201229939</v>
       </c>
     </row>
     <row r="55">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.1492323245365204</v>
+        <v>0.1492323245365203</v>
       </c>
       <c r="C55">
-        <v>0.6501752641389626</v>
+        <v>0.6345473358092539</v>
       </c>
       <c r="D55">
-        <v>0.3290543848148357</v>
+        <v>0.3139510802641049</v>
       </c>
       <c r="E55">
-        <v>-0.4957024186555411</v>
+        <v>-0.4661004856885689</v>
       </c>
       <c r="F55">
-        <v>0.7941670677285818</v>
+        <v>0.7645651347616094</v>
       </c>
     </row>
     <row r="56">
@@ -1585,16 +1585,16 @@
         <v>-0.1781668970719518</v>
       </c>
       <c r="C56">
-        <v>0.4789307986914075</v>
+        <v>0.4608968474549062</v>
       </c>
       <c r="D56">
-        <v>0.2516398842920961</v>
+        <v>0.2416245409943739</v>
       </c>
       <c r="E56">
-        <v>-0.6713720073582865</v>
+        <v>-0.6517422952019464</v>
       </c>
       <c r="F56">
-        <v>0.3150382132143829</v>
+        <v>0.2954085010580428</v>
       </c>
     </row>
     <row r="57">
@@ -1607,16 +1607,16 @@
         <v>-0.2067048972903257</v>
       </c>
       <c r="C57">
-        <v>0.3996920400822335</v>
+        <v>0.3832053776962288</v>
       </c>
       <c r="D57">
-        <v>0.2454427995141817</v>
+        <v>0.237045405733187</v>
       </c>
       <c r="E57">
-        <v>-0.6877639446028068</v>
+        <v>-0.6713053552280566</v>
       </c>
       <c r="F57">
-        <v>0.2743541500221554</v>
+        <v>0.257895560647405</v>
       </c>
     </row>
     <row r="58">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.0789079386190856</v>
+        <v>-0.07890793861908553</v>
       </c>
       <c r="C58">
-        <v>0.743550266569267</v>
+        <v>0.7238922545400983</v>
       </c>
       <c r="D58">
-        <v>0.2411939750415756</v>
+        <v>0.2233696385553825</v>
       </c>
       <c r="E58">
-        <v>-0.5516394429886263</v>
+        <v>-0.5167043854273646</v>
       </c>
       <c r="F58">
-        <v>0.3938235657504551</v>
+        <v>0.3588885081891935</v>
       </c>
     </row>
     <row r="59">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.009210911489691146</v>
+        <v>-0.009210911489691064</v>
       </c>
       <c r="C59">
-        <v>0.9684754120327213</v>
+        <v>0.9683976199933102</v>
       </c>
       <c r="D59">
-        <v>0.2330666916473211</v>
+        <v>0.232492678324531</v>
       </c>
       <c r="E59">
-        <v>-0.4660132331143427</v>
+        <v>-0.4648881876750277</v>
       </c>
       <c r="F59">
-        <v>0.4475914101349603</v>
+        <v>0.4464663646956456</v>
       </c>
     </row>
     <row r="60">
@@ -1673,16 +1673,16 @@
         <v>-0.1135880618417342</v>
       </c>
       <c r="C60">
-        <v>0.6643152983077898</v>
+        <v>0.6506067674183589</v>
       </c>
       <c r="D60">
-        <v>0.2617459501601322</v>
+        <v>0.2507908850019372</v>
       </c>
       <c r="E60">
-        <v>-0.6266006972548093</v>
+        <v>-0.6051291640964575</v>
       </c>
       <c r="F60">
-        <v>0.3994245735713408</v>
+        <v>0.377953040412989</v>
       </c>
     </row>
     <row r="61">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.003996642539649838</v>
+        <v>-0.003996642539649798</v>
       </c>
       <c r="C61">
-        <v>0.9847184894632064</v>
+        <v>0.984513526071348</v>
       </c>
       <c r="D61">
-        <v>0.2086615979920842</v>
+        <v>0.2058996229576655</v>
       </c>
       <c r="E61">
-        <v>-0.41296585956071</v>
+        <v>-0.4075524879670506</v>
       </c>
       <c r="F61">
-        <v>0.4049725744814104</v>
+        <v>0.3995592028877509</v>
       </c>
     </row>
     <row r="62">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.01900875184648694</v>
+        <v>0.01900875184648685</v>
       </c>
       <c r="C62">
-        <v>0.9263983389001405</v>
+        <v>0.9273358479770837</v>
       </c>
       <c r="D62">
-        <v>0.2057731562242262</v>
+        <v>0.208435546952418</v>
       </c>
       <c r="E62">
-        <v>-0.3842992233381304</v>
+        <v>-0.3895174132781598</v>
       </c>
       <c r="F62">
-        <v>0.4223167270311043</v>
+        <v>0.4275349169711335</v>
       </c>
     </row>
     <row r="63">
@@ -1739,16 +1739,16 @@
         <v>0.3248779082599003</v>
       </c>
       <c r="C63">
-        <v>0.09702538956593743</v>
+        <v>0.1097281479806345</v>
       </c>
       <c r="D63">
-        <v>0.1957745898175448</v>
+        <v>0.203122803045402</v>
       </c>
       <c r="E63">
-        <v>-0.05883323687058944</v>
+        <v>-0.07323547014791026</v>
       </c>
       <c r="F63">
-        <v>0.70858905339039</v>
+        <v>0.7229912866677108</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.0812681520682452</v>
+        <v>0.08126815206824506</v>
       </c>
       <c r="C64">
-        <v>0.7088308418220088</v>
+        <v>0.7144787872784637</v>
       </c>
       <c r="D64">
-        <v>0.2176280854854236</v>
+        <v>0.2221366182405988</v>
       </c>
       <c r="E64">
-        <v>-0.345275057507589</v>
+        <v>-0.3541116193308516</v>
       </c>
       <c r="F64">
-        <v>0.5078113616440794</v>
+        <v>0.5166479234673418</v>
       </c>
     </row>
     <row r="65">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.08011919273917413</v>
+        <v>0.0801191927391737</v>
       </c>
       <c r="C65">
-        <v>0.7353343487265993</v>
+        <v>0.7544481704304151</v>
       </c>
       <c r="D65">
-        <v>0.2370121965334137</v>
+        <v>0.2561522918259955</v>
       </c>
       <c r="E65">
-        <v>-0.3844161763630456</v>
+        <v>-0.421930073797171</v>
       </c>
       <c r="F65">
-        <v>0.5446545618413938</v>
+        <v>0.5821684592755183</v>
       </c>
     </row>
     <row r="66">
@@ -1802,19 +1802,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.03089044948929331</v>
+        <v>0.03089044948929309</v>
       </c>
       <c r="C66">
-        <v>0.8739071533580121</v>
+        <v>0.8609279501233056</v>
       </c>
       <c r="D66">
-        <v>0.1946497960444648</v>
+        <v>0.1763223518252184</v>
       </c>
       <c r="E66">
-        <v>-0.3506161403559245</v>
+        <v>-0.3146950097575351</v>
       </c>
       <c r="F66">
-        <v>0.4123970393345112</v>
+        <v>0.3764759087361212</v>
       </c>
     </row>
   </sheetData>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.01013106876417046</v>
+        <v>-0.0101310687641704</v>
       </c>
       <c r="C2">
-        <v>0.957526228699372</v>
+        <v>0.9564677349972461</v>
       </c>
       <c r="D2">
-        <v>0.1902257177836152</v>
+        <v>0.1855959199735235</v>
       </c>
       <c r="E2">
-        <v>-0.3829666245533366</v>
+        <v>-0.3738923875898544</v>
       </c>
       <c r="F2">
-        <v>0.3627044870249956</v>
+        <v>0.3536302500615136</v>
       </c>
     </row>
   </sheetData>
